--- a/archives/update_cards.xlsx
+++ b/archives/update_cards.xlsx
@@ -454,7 +454,11 @@
           <t>30439 PEDIDO AVULSO</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -472,7 +476,11 @@
           <t>30911 PED AVULSO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
